--- a/data/trans_orig/IQ28_P-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_P-Edad-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Peso medio, en kilogramos, recogido tras medición</t>
+          <t>Peso medio, en kilogramos, recogido tras medición (tasa de respuesta: 93,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,94; 14,98</t>
+          <t>12,94; 14,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,6; 13,75</t>
+          <t>12,63; 13,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,93; 27,52</t>
+          <t>16,34; 27,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,35; 14,91</t>
+          <t>13,4; 14,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,22; 14,87</t>
+          <t>13,26; 15,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,74; 20,65</t>
+          <t>14,83; 20,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,3; 14,54</t>
+          <t>13,28; 14,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,04; 14,17</t>
+          <t>13,02; 14,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,57; 23,02</t>
+          <t>16,57; 23,09</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,47; 22,79</t>
+          <t>21,42; 22,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,2; 22,67</t>
+          <t>21,21; 22,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,39; 26,69</t>
+          <t>22,48; 26,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,14; 23,37</t>
+          <t>22,16; 23,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,48; 22,75</t>
+          <t>21,52; 22,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,91; 29,73</t>
+          <t>24,92; 29,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,95; 22,92</t>
+          <t>21,98; 22,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,56; 22,44</t>
+          <t>21,55; 22,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,33; 27,43</t>
+          <t>24,3; 27,67</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,19; 38,76</t>
+          <t>36,37; 38,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,23; 37,42</t>
+          <t>35,32; 37,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,48; 39,78</t>
+          <t>33,38; 39,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36,06; 38,17</t>
+          <t>35,99; 38,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,32; 38,5</t>
+          <t>36,4; 38,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,68; 42,92</t>
+          <t>37,63; 42,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,46; 38,16</t>
+          <t>36,5; 38,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36,11; 37,59</t>
+          <t>36,1; 37,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,57; 40,73</t>
+          <t>36,63; 40,58</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50,52; 53,3</t>
+          <t>50,55; 53,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50,16; 52,93</t>
+          <t>50,27; 52,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,28; 55,79</t>
+          <t>46,17; 56,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55,19; 58,44</t>
+          <t>55,2; 58,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>53,83; 57,22</t>
+          <t>53,85; 57,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,19; 55,22</t>
+          <t>48,33; 54,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,29; 55,53</t>
+          <t>53,32; 55,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>52,4; 54,57</t>
+          <t>52,51; 54,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48,57; 54,43</t>
+          <t>48,35; 54,01</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>33,02; 35,16</t>
+          <t>33,07; 35,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>33,25; 35,31</t>
+          <t>33,28; 35,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,17; 46,03</t>
+          <t>36,26; 45,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34,33; 36,62</t>
+          <t>34,34; 36,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,92; 36,02</t>
+          <t>33,95; 36,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,76; 42,84</t>
+          <t>38,64; 42,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,0; 35,5</t>
+          <t>34,05; 35,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>33,94; 35,45</t>
+          <t>33,88; 35,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,19; 43,09</t>
+          <t>38,18; 43,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_P-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_P-Edad-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Peso medio, en kilogramos, recogido tras medición (tasa de respuesta: 93,67%)</t>
+          <t>Peso medio, en kilogramos, recogido por medición (tasa de respuesta: 93,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,94; 14,88</t>
+          <t>12,91; 14,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,63; 13,74</t>
+          <t>12,61; 13,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,34; 27,08</t>
+          <t>16,62; 27,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,4; 14,83</t>
+          <t>13,39; 14,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,26; 15,03</t>
+          <t>13,23; 14,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,83; 20,79</t>
+          <t>15,03; 20,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,28; 14,49</t>
+          <t>13,32; 14,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,02; 14,04</t>
+          <t>13,07; 14,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,57; 23,09</t>
+          <t>16,6; 23,14</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,42; 22,75</t>
+          <t>21,41; 22,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,21; 22,56</t>
+          <t>21,16; 22,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,48; 26,71</t>
+          <t>22,28; 26,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,16; 23,46</t>
+          <t>22,15; 23,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,52; 22,7</t>
+          <t>21,5; 22,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,92; 29,91</t>
+          <t>24,76; 29,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,98; 22,92</t>
+          <t>21,94; 22,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,55; 22,47</t>
+          <t>21,53; 22,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,3; 27,67</t>
+          <t>24,26; 27,63</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,37; 38,99</t>
+          <t>36,35; 38,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,32; 37,58</t>
+          <t>35,31; 37,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,38; 39,74</t>
+          <t>33,34; 39,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35,99; 38,16</t>
+          <t>36,02; 38,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,4; 38,67</t>
+          <t>36,29; 38,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,63; 42,7</t>
+          <t>37,76; 43,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,5; 38,17</t>
+          <t>36,4; 38,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36,1; 37,69</t>
+          <t>36,22; 37,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,63; 40,58</t>
+          <t>36,64; 40,76</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50,55; 53,32</t>
+          <t>50,5; 53,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50,27; 52,92</t>
+          <t>50,28; 52,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,17; 56,14</t>
+          <t>46,32; 56,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55,2; 58,46</t>
+          <t>55,12; 58,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>53,85; 57,11</t>
+          <t>53,73; 57,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,33; 54,9</t>
+          <t>48,29; 55,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,32; 55,52</t>
+          <t>53,36; 55,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>52,51; 54,77</t>
+          <t>52,47; 54,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48,35; 54,01</t>
+          <t>48,47; 54,45</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>33,07; 35,17</t>
+          <t>32,85; 35,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>33,28; 35,26</t>
+          <t>33,24; 35,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,26; 45,96</t>
+          <t>36,26; 46,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34,34; 36,69</t>
+          <t>34,36; 36,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,95; 36,18</t>
+          <t>33,86; 36,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,64; 42,94</t>
+          <t>38,81; 42,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,05; 35,59</t>
+          <t>34,06; 35,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>33,88; 35,38</t>
+          <t>33,9; 35,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,18; 43,06</t>
+          <t>38,35; 43,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_P-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_P-Edad-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13,93</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13,79</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17,37</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>13,67</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>13,13</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20,76</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13,93</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,79</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,06</t>
+          <t>20,78</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19,21</t>
+          <t>19,49</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,91; 14,86</t>
+          <t>13,35; 14,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,61; 13,81</t>
+          <t>13,22; 14,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,62; 27,93</t>
+          <t>14,73; 21,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,39; 14,77</t>
+          <t>12,94; 14,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,23; 14,82</t>
+          <t>12,6; 13,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,03; 20,6</t>
+          <t>17,07; 27,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,32; 14,52</t>
+          <t>13,3; 14,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,07; 14,11</t>
+          <t>13,04; 14,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,6; 23,14</t>
+          <t>16,69; 23,46</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>22,73</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22,05</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>26,98</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>22,08</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>21,89</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>24,23</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>22,73</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>22,05</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,97</t>
+          <t>24,73</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25,83</t>
+          <t>26,03</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,41; 22,7</t>
+          <t>22,14; 23,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,16; 22,6</t>
+          <t>21,48; 22,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,28; 26,48</t>
+          <t>25,06; 29,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,15; 23,4</t>
+          <t>21,47; 22,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,5; 22,74</t>
+          <t>21,2; 22,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,76; 29,42</t>
+          <t>22,9; 27,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,94; 22,88</t>
+          <t>21,95; 22,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,53; 22,47</t>
+          <t>21,56; 22,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,26; 27,63</t>
+          <t>24,63; 27,62</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>37,05</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>37,43</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>40,44</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>37,52</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>36,34</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>36,38</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>37,05</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>37,43</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,15</t>
+          <t>36,16</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>38,54</t>
+          <t>38,58</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,35; 38,83</t>
+          <t>36,06; 38,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,31; 37,51</t>
+          <t>36,32; 38,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,34; 39,65</t>
+          <t>37,87; 43,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36,02; 38,25</t>
+          <t>36,19; 38,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,29; 38,6</t>
+          <t>35,23; 37,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,76; 43,27</t>
+          <t>33,52; 39,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,4; 38,17</t>
+          <t>36,46; 38,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36,22; 37,69</t>
+          <t>36,11; 37,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,64; 40,76</t>
+          <t>36,66; 40,69</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>56,83</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>55,44</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>52,18</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>51,85</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>51,52</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>50,13</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>56,83</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>55,44</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,59</t>
+          <t>47,5</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>50,88</t>
+          <t>50,07</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50,5; 53,41</t>
+          <t>55,19; 58,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50,28; 52,9</t>
+          <t>53,83; 57,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,32; 56,22</t>
+          <t>49,07; 55,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55,12; 58,45</t>
+          <t>50,52; 53,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>53,73; 57,21</t>
+          <t>50,16; 52,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,29; 55,33</t>
+          <t>45,12; 49,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,36; 55,47</t>
+          <t>53,29; 55,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>52,47; 54,66</t>
+          <t>52,4; 54,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48,47; 54,45</t>
+          <t>48,01; 52,23</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>35,45</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>34,98</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>41,57</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>34,06</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>34,29</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>39,24</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>35,45</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>34,98</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40,67</t>
+          <t>37,67</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>40,02</t>
+          <t>39,83</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>32,85; 35,06</t>
+          <t>34,33; 36,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>33,24; 35,3</t>
+          <t>33,92; 36,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,26; 46,47</t>
+          <t>39,65; 43,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34,36; 36,64</t>
+          <t>33,02; 35,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,86; 36,12</t>
+          <t>33,25; 35,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,81; 42,98</t>
+          <t>35,93; 39,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,06; 35,59</t>
+          <t>34,0; 35,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>33,9; 35,41</t>
+          <t>33,94; 35,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,35; 43,54</t>
+          <t>38,44; 41,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_P-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_P-Edad-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -622,329 +627,217 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>13,93</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13,79</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17,37</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13,67</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,13</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20,78</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,78</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13,45</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>19,49</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>13.92534360774128</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>13.7880538254308</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>17.36554858637367</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>13.66700249593465</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>13.12519755800536</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>20.77725400780685</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>13.78405553829668</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>13.4509287240984</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>19.48700405801105</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>13,35; 14,91</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>13,22; 14,87</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14,73; 21,44</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>12,94; 14,98</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>12,6; 13,75</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17,07; 27,57</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>13,3; 14,54</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13,04; 14,17</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16,69; 23,46</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>13.34777788720086</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>13.22299286739472</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>14.72667090684147</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>12.93903030156038</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>12.59724223660972</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>17.07463837873864</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>13.29771318591343</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>13.04311995464289</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>16.68764166850122</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>14.90862317874506</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>14.86912455260781</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>21.43588422671504</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>14.984479816653</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>13.74794085906588</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>27.57032350975517</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>14.53537097215402</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>14.16644728868739</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>23.46342855250741</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>22,73</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>22,05</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>26,98</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>22,08</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>21,89</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>24,73</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>22,43</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>21,98</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>26,03</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>22,14; 23,37</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>21,48; 22,75</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>25,06; 29,61</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>21,47; 22,79</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>21,2; 22,67</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>22,9; 27,4</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>21,95; 22,92</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>21,56; 22,44</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>24,63; 27,62</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>22.73050630736817</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>22.05341040248159</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>26.98471076427703</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>22.08117889175119</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>21.89179489136074</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>24.73348014982524</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>22.42536449681487</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>21.98166970417679</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>26.02558720812901</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>37,05</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>37,43</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>40,44</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>37,52</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>36,34</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>36,16</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>37,28</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>36,88</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>38,58</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>22.13732502733445</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>21.47867453047471</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>25.05608534974834</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>21.47205578252879</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>21.19586411746249</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>22.89524288994466</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>21.9477029547618</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>21.55880381746213</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>24.63335810739854</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>36,06; 38,17</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>36,32; 38,5</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>37,87; 43,36</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>36,19; 38,76</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>35,23; 37,42</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>33,52; 39,22</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>36,46; 38,16</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>36,11; 37,59</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>36,66; 40,69</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>23.36540387898337</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>22.74609360756567</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>29.60708979560105</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>22.78723133777833</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>22.67369544620258</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>27.40342954441718</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>22.91736157526385</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>22.44040136992556</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>27.61826543286675</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -952,217 +845,324 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>56,83</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>55,44</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>52,18</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>51,85</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>51,52</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>47,5</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>54,37</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>53,52</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>50,07</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>37.04974904034714</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>37.43374231886899</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>40.43662518803056</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>37.51903730819239</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>36.33598834081146</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>36.15868563965934</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>37.28322804700512</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>36.88023940230217</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>38.58468159792688</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>55,19; 58,44</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>53,83; 57,22</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>49,07; 55,51</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>50,52; 53,3</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>50,16; 52,93</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>45,12; 49,95</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>53,29; 55,53</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>52,4; 54,57</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>48,01; 52,23</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>36.0594326615205</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>36.32341977258633</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>37.86895532641536</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>36.19454817636603</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>35.23415330193661</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>33.52352906438227</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>36.45637196333951</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>36.1083037599596</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>36.66312204565602</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>38.17306752484293</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>38.49852401079757</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>43.36335654336875</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>38.75980300667359</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>37.42167405104929</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>39.22286226880327</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>38.1597462098981</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>37.59073326631283</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>40.68622216471554</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>56.83136708755547</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>55.43619966068021</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>52.17667950875276</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>51.84623706778306</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>51.51514488866905</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>47.49552761204962</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>54.37465991481818</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>53.51970816621167</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>50.07431504131323</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>55.18862454216625</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>53.8267340512382</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>49.07125047935433</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>50.52276547427402</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>50.15641620852097</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>45.12460109458638</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>53.2853406383852</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>52.39528224332323</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>48.01427651315193</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>58.43710559234554</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>57.22303385167277</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>55.5102129295641</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>53.30334169490592</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>52.9265716084</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>49.95126063153993</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>55.53278353660183</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>54.56946128219379</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>52.23334826607044</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>35,45</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>34,98</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>41,57</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>34,06</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>34,29</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>37,67</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>34,77</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>34,65</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>39,83</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>34,33; 36,62</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>33,92; 36,02</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>39,65; 43,6</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>33,02; 35,16</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>33,25; 35,31</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>35,93; 39,45</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>34,0; 35,5</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>33,94; 35,45</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>38,44; 41,2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>35.44843435005416</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>34.98302810569339</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>41.57133812767115</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>34.05725872658873</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>34.28930529698515</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>37.67013959233078</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>34.76911694347378</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>34.65166167910315</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>39.83460484424268</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>34.3267834308165</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>33.92413600596117</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>39.64719022744256</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>33.01926233159483</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>33.25006435481784</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>35.92751210078502</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>33.99698655297402</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>33.93870104361312</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>38.44355676125927</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>36.61512912221778</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>36.01709270789181</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>43.59954962486894</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>35.16099858478962</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>35.3139747648505</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>39.44922824487214</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>35.49591031272644</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>35.45095558898304</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>41.19932662360646</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1171,14 +1171,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
